--- a/docs/사내톡_개발일정표.xlsx
+++ b/docs/사내톡_개발일정표.xlsx
@@ -13,7 +13,7 @@
     <sheet name="일별 커밋" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">개발일정표!$A$5:$K$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">개발일정표!$A$5:$K$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">개발일정표!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="192">
   <si>
     <t>사내톡 개발일정표</t>
   </si>
@@ -389,7 +389,28 @@
     <t>코드 주석 정확성 검수</t>
   </si>
   <si>
-    <t>MainForm.cs 대조 완료, 나머지 파일은 진행 중</t>
+    <t>MainForm.cs 대조, 코드 참조 전수 검사, 6곳 수정 완료. 다른 파일의 동작 설명은 미검증</t>
+  </si>
+  <si>
+    <t>데이터 정의서에 전체 컬럼 ERD 추가</t>
+  </si>
+  <si>
+    <t>데이터 정의서 v2 2.3절 (12개 테이블 모든 컬럼)</t>
+  </si>
+  <si>
+    <t>다른 포트(9100·19000) 접속 시험</t>
+  </si>
+  <si>
+    <t>SV-01, SC-01</t>
+  </si>
+  <si>
+    <t>TLS 1.3·ServerInfo 응답, 서비스 감독 방식 /quit 종료 확인</t>
+  </si>
+  <si>
+    <t>실행 화면 스크린샷 14장 자동 촬영·요구사항 분석서에 추가</t>
+  </si>
+  <si>
+    <t>docs/screenshots, 분석서 10장 (시연 계정 DEMO01~03·DEMOADM 사용)</t>
   </si>
   <si>
     <t>9. 마무리 (제안 일정)</t>
@@ -422,10 +443,16 @@
     <t>README 부하 측정표는 10만 회 기준 — 제안 일정</t>
   </si>
   <si>
+    <t>시연 시나리오 확정·시연 영상 촬영</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>docs/시연_시나리오.md 순서대로 — 제안 일정</t>
+  </si>
+  <si>
     <t>발표 자료 준비</t>
-  </si>
-  <si>
-    <t>—</t>
   </si>
   <si>
     <t>TLS 적용 전후 비교, 부하 테스트 결과 등 — 제안 일정</t>
@@ -972,7 +999,7 @@
                   <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8400000000000001</c:v>
+                  <c:v>0.925</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.0</c:v>
@@ -1558,7 +1585,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -2974,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="I41" s="10">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J41" s="11" t="str">
         <f>IF(I41&gt;=1,"완료",IF(I41&gt;0,"진행 중","예정"))</f>
@@ -2989,36 +3016,36 @@
         <v>37</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="D42" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F42" s="12">
-        <v>46329</v>
-      </c>
-      <c r="G42" s="12">
-        <v>46330</v>
+        <v>17</v>
+      </c>
+      <c r="F42" s="8">
+        <v>46328</v>
+      </c>
+      <c r="G42" s="8">
+        <v>46328</v>
       </c>
       <c r="H42" s="9">
         <f>G42-F42+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="11" t="str">
         <f>IF(I42&gt;=1,"완료",IF(I42&gt;0,"진행 중","예정"))</f>
-        <v>예정</v>
+        <v>완료</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3026,36 +3053,36 @@
         <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="12">
-        <v>46329</v>
-      </c>
-      <c r="G43" s="12">
-        <v>46330</v>
+        <v>17</v>
+      </c>
+      <c r="F43" s="8">
+        <v>46328</v>
+      </c>
+      <c r="G43" s="8">
+        <v>46328</v>
       </c>
       <c r="H43" s="9">
         <f>G43-F43+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="11" t="str">
         <f>IF(I43&gt;=1,"완료",IF(I43&gt;0,"진행 중","예정"))</f>
-        <v>예정</v>
+        <v>완료</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3063,36 +3090,36 @@
         <v>39</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F44" s="12">
-        <v>46330</v>
-      </c>
-      <c r="G44" s="12">
-        <v>46330</v>
+        <v>17</v>
+      </c>
+      <c r="F44" s="8">
+        <v>46328</v>
+      </c>
+      <c r="G44" s="8">
+        <v>46328</v>
       </c>
       <c r="H44" s="9">
         <f>G44-F44+1</f>
         <v>1</v>
       </c>
       <c r="I44" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="11" t="str">
         <f>IF(I44&gt;=1,"완료",IF(I44&gt;0,"진행 중","예정"))</f>
-        <v>예정</v>
+        <v>완료</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3100,22 +3127,22 @@
         <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F45" s="12">
+        <v>46329</v>
+      </c>
+      <c r="G45" s="12">
         <v>46330</v>
-      </c>
-      <c r="G45" s="12">
-        <v>46331</v>
       </c>
       <c r="H45" s="9">
         <f>G45-F45+1</f>
@@ -3129,7 +3156,7 @@
         <v>예정</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3137,26 +3164,26 @@
         <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F46" s="12">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="G46" s="12">
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="H46" s="9">
         <f>G46-F46+1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="10">
         <v>0</v>
@@ -3166,22 +3193,170 @@
         <v>예정</v>
       </c>
       <c r="K46" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>42</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>137</v>
       </c>
+      <c r="D47" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F47" s="12">
+        <v>46330</v>
+      </c>
+      <c r="G47" s="12">
+        <v>46330</v>
+      </c>
+      <c r="H47" s="9">
+        <f>G47-F47+1</f>
+        <v>1</v>
+      </c>
+      <c r="I47" s="10">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11" t="str">
+        <f>IF(I47&gt;=1,"완료",IF(I47&gt;0,"진행 중","예정"))</f>
+        <v>예정</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C48" s="13" t="s">
-        <v>138</v>
+      <c r="A48" s="5">
+        <v>43</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F48" s="12">
+        <v>46330</v>
+      </c>
+      <c r="G48" s="12">
+        <v>46331</v>
+      </c>
+      <c r="H48" s="9">
+        <f>G48-F48+1</f>
+        <v>2</v>
+      </c>
+      <c r="I48" s="10">
+        <v>0</v>
+      </c>
+      <c r="J48" s="11" t="str">
+        <f>IF(I48&gt;=1,"완료",IF(I48&gt;0,"진행 중","예정"))</f>
+        <v>예정</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>44</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="12">
+        <v>46330</v>
+      </c>
+      <c r="G49" s="12">
+        <v>46331</v>
+      </c>
+      <c r="H49" s="9">
+        <f>G49-F49+1</f>
+        <v>2</v>
+      </c>
+      <c r="I49" s="10">
+        <v>0</v>
+      </c>
+      <c r="J49" s="11" t="str">
+        <f>IF(I49&gt;=1,"완료",IF(I49&gt;0,"진행 중","예정"))</f>
+        <v>예정</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>45</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F50" s="12">
+        <v>46332</v>
+      </c>
+      <c r="G50" s="12">
+        <v>46332</v>
+      </c>
+      <c r="H50" s="9">
+        <f>G50-F50+1</f>
+        <v>1</v>
+      </c>
+      <c r="I50" s="10">
+        <v>0</v>
+      </c>
+      <c r="J50" s="11" t="str">
+        <f>IF(I50&gt;=1,"완료",IF(I50&gt;0,"진행 중","예정"))</f>
+        <v>예정</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C52" s="13" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K46"/>
+  <autoFilter ref="A5:K50"/>
   <mergeCells count="3">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J46">
+  <conditionalFormatting sqref="J6:J50">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"완료"</formula>
     </cfRule>
@@ -3192,7 +3367,7 @@
       <formula>"예정"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:I46">
+  <conditionalFormatting sqref="I6:I50">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -3207,14 +3382,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="진척률" error="0%~100% 사이로 입력하세요." sqref="I6:I46">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="진척률" error="0%~100% 사이로 입력하세요." sqref="I6:I50">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E50">
       <formula1>"박은정,반재영,장선화,팀 전체,미정"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="종료일" error="종료일은 시작일보다 빠를 수 없습니다." sqref="G6:G46">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="종료일" error="종료일은 시작일보다 빠를 수 없습니다." sqref="G6:G50">
       <formula1>G6&gt;=F6</formula1>
     </dataValidation>
   </dataValidations>
@@ -3238,7 +3413,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>I6:I46</xm:sqref>
+          <xm:sqref>I6:I50</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3251,7 +3426,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -3263,7 +3438,7 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3286,7 +3461,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3315,10 +3490,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>12</v>
@@ -6194,19 +6369,19 @@
       </c>
       <c r="B41" s="16" t="str">
         <f>'개발일정표'!C42</f>
-        <v>미확인 테스트 실행·결과 기록 (T-03~T-08, T-10, T-16)</v>
+        <v>데이터 정의서에 전체 컬럼 ERD 추가</v>
       </c>
       <c r="C41" s="17">
         <f>'개발일정표'!F42</f>
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="D41" s="17">
         <f>'개발일정표'!G42</f>
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="E41" s="15" t="str">
         <f>'개발일정표'!J42</f>
-        <v>예정</v>
+        <v>완료</v>
       </c>
       <c r="F41" s="18">
         <f>IF(AND(F$4&gt;=$C41,F$4&lt;=$D41),1,"")</f>
@@ -6234,15 +6409,15 @@
       </c>
       <c r="L41" s="18">
         <f>IF(AND(L$4&gt;=$C41,L$4&lt;=$D41),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M41" s="18">
         <f>IF(AND(M$4&gt;=$C41,M$4&lt;=$D41),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N41" s="18">
         <f>IF(AND(N$4&gt;=$C41,N$4&lt;=$D41),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="O41" s="18">
         <f>IF(AND(O$4&gt;=$C41,O$4&lt;=$D41),1,"")</f>
@@ -6272,19 +6447,19 @@
       </c>
       <c r="B42" s="16" t="str">
         <f>'개발일정표'!C43</f>
-        <v>서버 PC 실환경 확인 (서비스 설치·권한 제한·환경 변수·부팅 자동 시작)</v>
+        <v>다른 포트(9100·19000) 접속 시험</v>
       </c>
       <c r="C42" s="17">
         <f>'개발일정표'!F43</f>
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="D42" s="17">
         <f>'개발일정표'!G43</f>
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="E42" s="15" t="str">
         <f>'개발일정표'!J43</f>
-        <v>예정</v>
+        <v>완료</v>
       </c>
       <c r="F42" s="18">
         <f>IF(AND(F$4&gt;=$C42,F$4&lt;=$D42),1,"")</f>
@@ -6312,15 +6487,15 @@
       </c>
       <c r="L42" s="18">
         <f>IF(AND(L$4&gt;=$C42,L$4&lt;=$D42),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M42" s="18">
         <f>IF(AND(M$4&gt;=$C42,M$4&lt;=$D42),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N42" s="18">
         <f>IF(AND(N$4&gt;=$C42,N$4&lt;=$D42),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="O42" s="18">
         <f>IF(AND(O$4&gt;=$C42,O$4&lt;=$D42),1,"")</f>
@@ -6350,19 +6525,19 @@
       </c>
       <c r="B43" s="16" t="str">
         <f>'개발일정표'!C44</f>
-        <v>60만 회 해시 기준 부하 테스트 재측정</v>
+        <v>실행 화면 스크린샷 14장 자동 촬영·요구사항 분석서에 추가</v>
       </c>
       <c r="C43" s="17">
         <f>'개발일정표'!F44</f>
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="D43" s="17">
         <f>'개발일정표'!G44</f>
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="E43" s="15" t="str">
         <f>'개발일정표'!J44</f>
-        <v>예정</v>
+        <v>완료</v>
       </c>
       <c r="F43" s="18">
         <f>IF(AND(F$4&gt;=$C43,F$4&lt;=$D43),1,"")</f>
@@ -6390,7 +6565,7 @@
       </c>
       <c r="L43" s="18">
         <f>IF(AND(L$4&gt;=$C43,L$4&lt;=$D43),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M43" s="18">
         <f>IF(AND(M$4&gt;=$C43,M$4&lt;=$D43),1,"")</f>
@@ -6398,7 +6573,7 @@
       </c>
       <c r="N43" s="18">
         <f>IF(AND(N$4&gt;=$C43,N$4&lt;=$D43),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="O43" s="18">
         <f>IF(AND(O$4&gt;=$C43,O$4&lt;=$D43),1,"")</f>
@@ -6428,15 +6603,15 @@
       </c>
       <c r="B44" s="16" t="str">
         <f>'개발일정표'!C45</f>
-        <v>발표 자료 준비</v>
+        <v>미확인 테스트 실행·결과 기록 (T-03~T-08, T-10, T-16)</v>
       </c>
       <c r="C44" s="17">
         <f>'개발일정표'!F45</f>
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="D44" s="17">
         <f>'개발일정표'!G45</f>
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E44" s="15" t="str">
         <f>'개발일정표'!J45</f>
@@ -6472,7 +6647,7 @@
       </c>
       <c r="M44" s="18">
         <f>IF(AND(M$4&gt;=$C44,M$4&lt;=$D44),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N44" s="18">
         <f>IF(AND(N$4&gt;=$C44,N$4&lt;=$D44),1,"")</f>
@@ -6480,7 +6655,7 @@
       </c>
       <c r="O44" s="18">
         <f>IF(AND(O$4&gt;=$C44,O$4&lt;=$D44),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="P44" s="18">
         <f>IF(AND(P$4&gt;=$C44,P$4&lt;=$D44),1,"")</f>
@@ -6506,15 +6681,15 @@
       </c>
       <c r="B45" s="16" t="str">
         <f>'개발일정표'!C46</f>
-        <v>최종 점검·제출</v>
+        <v>서버 PC 실환경 확인 (서비스 설치·권한 제한·환경 변수·부팅 자동 시작)</v>
       </c>
       <c r="C45" s="17">
         <f>'개발일정표'!F46</f>
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="D45" s="17">
         <f>'개발일정표'!G46</f>
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="E45" s="15" t="str">
         <f>'개발일정표'!J46</f>
@@ -6550,11 +6725,11 @@
       </c>
       <c r="M45" s="18">
         <f>IF(AND(M$4&gt;=$C45,M$4&lt;=$D45),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N45" s="18">
         <f>IF(AND(N$4&gt;=$C45,N$4&lt;=$D45),1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O45" s="18">
         <f>IF(AND(O$4&gt;=$C45,O$4&lt;=$D45),1,"")</f>
@@ -6562,7 +6737,7 @@
       </c>
       <c r="P45" s="18">
         <f>IF(AND(P$4&gt;=$C45,P$4&lt;=$D45),1,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q45" s="18">
         <f>IF(AND(Q$4&gt;=$C45,Q$4&lt;=$D45),1,"")</f>
@@ -6574,6 +6749,318 @@
       </c>
       <c r="S45" s="18">
         <f>IF(AND(S$4&gt;=$C45,S$4&lt;=$D45),1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
+      <c r="A46" s="15">
+        <f>'개발일정표'!A47</f>
+        <v>42</v>
+      </c>
+      <c r="B46" s="16" t="str">
+        <f>'개발일정표'!C47</f>
+        <v>60만 회 해시 기준 부하 테스트 재측정</v>
+      </c>
+      <c r="C46" s="17">
+        <f>'개발일정표'!F47</f>
+        <v>46330</v>
+      </c>
+      <c r="D46" s="17">
+        <f>'개발일정표'!G47</f>
+        <v>46330</v>
+      </c>
+      <c r="E46" s="15" t="str">
+        <f>'개발일정표'!J47</f>
+        <v>예정</v>
+      </c>
+      <c r="F46" s="18">
+        <f>IF(AND(F$4&gt;=$C46,F$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="18">
+        <f>IF(AND(G$4&gt;=$C46,G$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="18">
+        <f>IF(AND(H$4&gt;=$C46,H$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="18">
+        <f>IF(AND(I$4&gt;=$C46,I$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="18">
+        <f>IF(AND(J$4&gt;=$C46,J$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="18">
+        <f>IF(AND(K$4&gt;=$C46,K$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="18">
+        <f>IF(AND(L$4&gt;=$C46,L$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="18">
+        <f>IF(AND(M$4&gt;=$C46,M$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="N46" s="18">
+        <f>IF(AND(N$4&gt;=$C46,N$4&lt;=$D46),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="O46" s="18">
+        <f>IF(AND(O$4&gt;=$C46,O$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="P46" s="18">
+        <f>IF(AND(P$4&gt;=$C46,P$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="Q46" s="18">
+        <f>IF(AND(Q$4&gt;=$C46,Q$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="R46" s="18">
+        <f>IF(AND(R$4&gt;=$C46,R$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+      <c r="S46" s="18">
+        <f>IF(AND(S$4&gt;=$C46,S$4&lt;=$D46),1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="A47" s="15">
+        <f>'개발일정표'!A48</f>
+        <v>43</v>
+      </c>
+      <c r="B47" s="16" t="str">
+        <f>'개발일정표'!C48</f>
+        <v>시연 시나리오 확정·시연 영상 촬영</v>
+      </c>
+      <c r="C47" s="17">
+        <f>'개발일정표'!F48</f>
+        <v>46330</v>
+      </c>
+      <c r="D47" s="17">
+        <f>'개발일정표'!G48</f>
+        <v>46331</v>
+      </c>
+      <c r="E47" s="15" t="str">
+        <f>'개발일정표'!J48</f>
+        <v>예정</v>
+      </c>
+      <c r="F47" s="18">
+        <f>IF(AND(F$4&gt;=$C47,F$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="18">
+        <f>IF(AND(G$4&gt;=$C47,G$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="18">
+        <f>IF(AND(H$4&gt;=$C47,H$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="18">
+        <f>IF(AND(I$4&gt;=$C47,I$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="18">
+        <f>IF(AND(J$4&gt;=$C47,J$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="18">
+        <f>IF(AND(K$4&gt;=$C47,K$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="18">
+        <f>IF(AND(L$4&gt;=$C47,L$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="18">
+        <f>IF(AND(M$4&gt;=$C47,M$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="N47" s="18">
+        <f>IF(AND(N$4&gt;=$C47,N$4&lt;=$D47),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="O47" s="18">
+        <f>IF(AND(O$4&gt;=$C47,O$4&lt;=$D47),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="P47" s="18">
+        <f>IF(AND(P$4&gt;=$C47,P$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="Q47" s="18">
+        <f>IF(AND(Q$4&gt;=$C47,Q$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="R47" s="18">
+        <f>IF(AND(R$4&gt;=$C47,R$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+      <c r="S47" s="18">
+        <f>IF(AND(S$4&gt;=$C47,S$4&lt;=$D47),1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" s="15">
+        <f>'개발일정표'!A49</f>
+        <v>44</v>
+      </c>
+      <c r="B48" s="16" t="str">
+        <f>'개발일정표'!C49</f>
+        <v>발표 자료 준비</v>
+      </c>
+      <c r="C48" s="17">
+        <f>'개발일정표'!F49</f>
+        <v>46330</v>
+      </c>
+      <c r="D48" s="17">
+        <f>'개발일정표'!G49</f>
+        <v>46331</v>
+      </c>
+      <c r="E48" s="15" t="str">
+        <f>'개발일정표'!J49</f>
+        <v>예정</v>
+      </c>
+      <c r="F48" s="18">
+        <f>IF(AND(F$4&gt;=$C48,F$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="18">
+        <f>IF(AND(G$4&gt;=$C48,G$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="18">
+        <f>IF(AND(H$4&gt;=$C48,H$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="18">
+        <f>IF(AND(I$4&gt;=$C48,I$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="18">
+        <f>IF(AND(J$4&gt;=$C48,J$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="K48" s="18">
+        <f>IF(AND(K$4&gt;=$C48,K$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="18">
+        <f>IF(AND(L$4&gt;=$C48,L$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="18">
+        <f>IF(AND(M$4&gt;=$C48,M$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="N48" s="18">
+        <f>IF(AND(N$4&gt;=$C48,N$4&lt;=$D48),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="O48" s="18">
+        <f>IF(AND(O$4&gt;=$C48,O$4&lt;=$D48),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="P48" s="18">
+        <f>IF(AND(P$4&gt;=$C48,P$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="Q48" s="18">
+        <f>IF(AND(Q$4&gt;=$C48,Q$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="R48" s="18">
+        <f>IF(AND(R$4&gt;=$C48,R$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+      <c r="S48" s="18">
+        <f>IF(AND(S$4&gt;=$C48,S$4&lt;=$D48),1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
+      <c r="A49" s="15">
+        <f>'개발일정표'!A50</f>
+        <v>45</v>
+      </c>
+      <c r="B49" s="16" t="str">
+        <f>'개발일정표'!C50</f>
+        <v>최종 점검·제출</v>
+      </c>
+      <c r="C49" s="17">
+        <f>'개발일정표'!F50</f>
+        <v>46332</v>
+      </c>
+      <c r="D49" s="17">
+        <f>'개발일정표'!G50</f>
+        <v>46332</v>
+      </c>
+      <c r="E49" s="15" t="str">
+        <f>'개발일정표'!J50</f>
+        <v>예정</v>
+      </c>
+      <c r="F49" s="18">
+        <f>IF(AND(F$4&gt;=$C49,F$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="18">
+        <f>IF(AND(G$4&gt;=$C49,G$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="18">
+        <f>IF(AND(H$4&gt;=$C49,H$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="18">
+        <f>IF(AND(I$4&gt;=$C49,I$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="18">
+        <f>IF(AND(J$4&gt;=$C49,J$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="18">
+        <f>IF(AND(K$4&gt;=$C49,K$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="18">
+        <f>IF(AND(L$4&gt;=$C49,L$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="18">
+        <f>IF(AND(M$4&gt;=$C49,M$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="N49" s="18">
+        <f>IF(AND(N$4&gt;=$C49,N$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="O49" s="18">
+        <f>IF(AND(O$4&gt;=$C49,O$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="P49" s="18">
+        <f>IF(AND(P$4&gt;=$C49,P$4&lt;=$D49),1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="Q49" s="18">
+        <f>IF(AND(Q$4&gt;=$C49,Q$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="R49" s="18">
+        <f>IF(AND(R$4&gt;=$C49,R$4&lt;=$D49),1,"")</f>
+        <v/>
+      </c>
+      <c r="S49" s="18">
+        <f>IF(AND(S$4&gt;=$C49,S$4&lt;=$D49),1,"")</f>
         <v/>
       </c>
     </row>
@@ -6582,7 +7069,7 @@
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:S45">
+  <conditionalFormatting sqref="F5:S49">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(F5=1,$E5="완료")</formula>
     </cfRule>
@@ -6615,7 +7102,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6625,7 +7112,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6635,61 +7122,61 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B4" s="9">
-        <f>COUNTA('개발일정표'!$A$6:$A$46)</f>
-        <v>41</v>
+        <f>COUNTA('개발일정표'!$A$6:$A$50)</f>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B5" s="9">
-        <f>COUNTIF('개발일정표'!$J$6:$J$46,"완료")</f>
-        <v>34</v>
+        <f>COUNTIF('개발일정표'!$J$6:$J$50,"완료")</f>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B6" s="9">
-        <f>COUNTIF('개발일정표'!$J$6:$J$46,"진행 중")</f>
+        <f>COUNTIF('개발일정표'!$J$6:$J$50,"진행 중")</f>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B7" s="9">
-        <f>COUNTIF('개발일정표'!$J$6:$J$46,"예정")</f>
-        <v>5</v>
+        <f>COUNTIF('개발일정표'!$J$6:$J$50,"예정")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B8" s="21">
         <f>B5/B4</f>
-        <v>0.8292682926829268</v>
+        <v>0.8222222222222222</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B9" s="21">
-        <f>AVERAGE('개발일정표'!$I$6:$I$46)</f>
-        <v>0.8585365853658538</v>
+        <f>AVERAGE('개발일정표'!$I$6:$I$50)</f>
+        <v>0.8533333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6697,22 +7184,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="22">
-        <f>MIN('개발일정표'!$F$6:$F$46)</f>
+        <f>MIN('개발일정표'!$F$6:$F$50)</f>
         <v>46322</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B11" s="22">
-        <f>MAX('개발일정표'!$G$6:$G$46)</f>
+        <f>MAX('개발일정표'!$G$6:$G$50)</f>
         <v>46332</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B12" s="9">
         <f>B11-B10+1</f>
@@ -6721,7 +7208,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6729,13 +7216,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6743,15 +7230,15 @@
         <v>14</v>
       </c>
       <c r="B16" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A16)</f>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A16)</f>
         <v>3</v>
       </c>
       <c r="C16" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A16,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A16,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>3</v>
       </c>
       <c r="D16" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A16,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A16,'개발일정표'!$I$6:$I$50)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -6760,15 +7247,15 @@
         <v>25</v>
       </c>
       <c r="B17" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A17)</f>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A17)</f>
         <v>2</v>
       </c>
       <c r="C17" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A17,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A17,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>2</v>
       </c>
       <c r="D17" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A17,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A17,'개발일정표'!$I$6:$I$50)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -6777,15 +7264,15 @@
         <v>32</v>
       </c>
       <c r="B18" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A18)</f>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A18)</f>
         <v>4</v>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A18,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A18,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>4</v>
       </c>
       <c r="D18" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A18,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A18,'개발일정표'!$I$6:$I$50)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -6794,15 +7281,15 @@
         <v>45</v>
       </c>
       <c r="B19" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A19)</f>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A19)</f>
         <v>3</v>
       </c>
       <c r="C19" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A19,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A19,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>3</v>
       </c>
       <c r="D19" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A19,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A19,'개발일정표'!$I$6:$I$50)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -6811,15 +7298,15 @@
         <v>54</v>
       </c>
       <c r="B20" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A20)</f>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A20)</f>
         <v>12</v>
       </c>
       <c r="C20" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A20,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A20,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>12</v>
       </c>
       <c r="D20" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A20,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A20,'개발일정표'!$I$6:$I$50)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -6828,15 +7315,15 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A21)</f>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A21)</f>
         <v>4</v>
       </c>
       <c r="C21" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A21,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A21,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>4</v>
       </c>
       <c r="D21" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A21,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A21,'개발일정표'!$I$6:$I$50)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -6845,15 +7332,15 @@
         <v>102</v>
       </c>
       <c r="B22" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A22)</f>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A22)</f>
         <v>3</v>
       </c>
       <c r="C22" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A22,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A22,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>3</v>
       </c>
       <c r="D22" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A22,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A22,'개발일정표'!$I$6:$I$50)</f>
         <v>1.0</v>
       </c>
     </row>
@@ -6862,51 +7349,51 @@
         <v>109</v>
       </c>
       <c r="B23" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A23)</f>
-        <v>5</v>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A23)</f>
+        <v>8</v>
       </c>
       <c r="C23" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A23,'개발일정표'!$J$6:$J$46,"완료")</f>
-        <v>3</v>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A23,'개발일정표'!$J$6:$J$50,"완료")</f>
+        <v>6</v>
       </c>
       <c r="D23" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A23,'개발일정표'!$I$6:$I$46)</f>
-        <v>0.8400000000000001</v>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A23,'개발일정표'!$I$6:$I$50)</f>
+        <v>0.925</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B24" s="9">
-        <f>COUNTIF('개발일정표'!$B$6:$B$46,A24)</f>
-        <v>5</v>
+        <f>COUNTIF('개발일정표'!$B$6:$B$50,A24)</f>
+        <v>6</v>
       </c>
       <c r="C24" s="9">
-        <f>COUNTIFS('개발일정표'!$B$6:$B$46,A24,'개발일정표'!$J$6:$J$46,"완료")</f>
+        <f>COUNTIFS('개발일정표'!$B$6:$B$50,A24,'개발일정표'!$J$6:$J$50,"완료")</f>
         <v>0</v>
       </c>
       <c r="D24" s="21">
-        <f>AVERAGEIF('개발일정표'!$B$6:$B$46,A24,'개발일정표'!$I$6:$I$46)</f>
+        <f>AVERAGEIF('개발일정표'!$B$6:$B$50,A24,'개발일정표'!$I$6:$I$50)</f>
         <v>0.0</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F28" s="4"/>
     </row>
@@ -6915,12 +7402,12 @@
         <v>46322</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F29" s="6"/>
     </row>
@@ -6929,12 +7416,12 @@
         <v>46323</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F30" s="6"/>
     </row>
@@ -6943,12 +7430,12 @@
         <v>46324</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F31" s="6"/>
     </row>
@@ -6957,12 +7444,12 @@
         <v>46327</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F32" s="6"/>
     </row>
@@ -6971,12 +7458,12 @@
         <v>46328</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F33" s="6"/>
     </row>
@@ -6985,18 +7472,18 @@
         <v>46332</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F34" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7072,27 +7559,27 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7103,7 +7590,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7114,7 +7601,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7125,7 +7612,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7147,7 +7634,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7158,19 +7645,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="20" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B11" s="11">
         <f>SUM(B5:B10)</f>
         <v>60</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
